--- a/Effort Tracking.xlsx
+++ b/Effort Tracking.xlsx
@@ -20,13 +20,13 @@
     <t>Summary of Tasks</t>
   </si>
   <si>
-    <t>Estimate (hours)</t>
-  </si>
-  <si>
-    <t>Non-coding Effort (hours)</t>
-  </si>
-  <si>
-    <t>Coding Effort (hours)</t>
+    <t>Estimate (mins)</t>
+  </si>
+  <si>
+    <t>Non-coding Effort (mins)</t>
+  </si>
+  <si>
+    <t>Coding Effort (mins)</t>
   </si>
   <si>
     <t>Estimator</t>
@@ -408,13 +408,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="D2" s="1">
         <v>0.0</v>
       </c>
       <c r="E2" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -431,13 +431,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>1.25</v>
+        <v>75.0</v>
       </c>
       <c r="D3" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="E3" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -454,13 +454,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="D4" s="1">
         <v>0.0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -477,13 +477,13 @@
         <v>11</v>
       </c>
       <c r="C5" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="D5" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="E5" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -500,13 +500,13 @@
         <v>12</v>
       </c>
       <c r="C6" s="1">
-        <v>0.25</v>
+        <v>15.0</v>
       </c>
       <c r="D6" s="1">
         <v>0.0</v>
       </c>
       <c r="E6" s="1">
-        <v>0.2</v>
+        <v>12.0</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>13</v>
@@ -523,13 +523,13 @@
         <v>14</v>
       </c>
       <c r="C7" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="D7" s="1">
-        <v>0.2</v>
+        <v>12.0</v>
       </c>
       <c r="E7" s="1">
-        <v>0.3</v>
+        <v>18.0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -546,13 +546,13 @@
         <v>15</v>
       </c>
       <c r="C8" s="1">
-        <v>2.0</v>
+        <v>120.0</v>
       </c>
       <c r="D8" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="E8" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>13</v>
@@ -569,13 +569,13 @@
         <v>16</v>
       </c>
       <c r="C9" s="1">
-        <v>1.5</v>
+        <v>90.0</v>
       </c>
       <c r="D9" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="E9" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>13</v>
@@ -592,13 +592,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="1">
-        <v>0.42</v>
+        <v>25.2</v>
       </c>
       <c r="D10" s="1">
         <v>0.0</v>
       </c>
       <c r="E10" s="1">
-        <v>0.42</v>
+        <v>25.2</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
@@ -615,13 +615,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="1">
-        <v>3.5</v>
+        <v>210.0</v>
       </c>
       <c r="D11" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="E11" s="1">
-        <v>3.0</v>
+        <v>180.0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>19</v>
@@ -638,13 +638,13 @@
         <v>20</v>
       </c>
       <c r="C12" s="1">
-        <v>1.5</v>
+        <v>90.0</v>
       </c>
       <c r="D12" s="1">
         <v>0.0</v>
       </c>
       <c r="E12" s="1">
-        <v>1.5</v>
+        <v>90.0</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>19</v>
@@ -661,13 +661,13 @@
         <v>21</v>
       </c>
       <c r="C13" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.2</v>
+        <v>12.0</v>
       </c>
       <c r="E13" s="1">
-        <v>0.8</v>
+        <v>48.0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>22</v>
@@ -684,13 +684,13 @@
         <v>23</v>
       </c>
       <c r="C14" s="1">
-        <v>2.0</v>
+        <v>120.0</v>
       </c>
       <c r="D14" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="E14" s="1">
-        <v>1.5</v>
+        <v>90.0</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>22</v>
@@ -707,13 +707,13 @@
         <v>24</v>
       </c>
       <c r="C15" s="1">
-        <v>2.0</v>
+        <v>120.0</v>
       </c>
       <c r="D15" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="E15" s="1">
-        <v>1.5</v>
+        <v>90.0</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>19</v>
@@ -730,13 +730,13 @@
         <v>25</v>
       </c>
       <c r="C16" s="1">
-        <v>0.5</v>
+        <v>30.0</v>
       </c>
       <c r="D16" s="1">
-        <v>0.25</v>
+        <v>15.0</v>
       </c>
       <c r="E16" s="1">
-        <v>0.25</v>
+        <v>15.0</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>19</v>
@@ -753,13 +753,13 @@
         <v>26</v>
       </c>
       <c r="C17" s="1">
-        <v>4.0</v>
+        <v>240.0</v>
       </c>
       <c r="D17" s="1">
-        <v>0.75</v>
+        <v>45.0</v>
       </c>
       <c r="E17" s="1">
-        <v>3.25</v>
+        <v>195.0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>19</v>
@@ -776,10 +776,10 @@
         <v>27</v>
       </c>
       <c r="C18" s="1">
-        <v>2.0</v>
+        <v>120.0</v>
       </c>
       <c r="D18" s="1">
-        <v>2.0</v>
+        <v>120.0</v>
       </c>
       <c r="E18" s="1">
         <v>0.0</v>
